--- a/ops-data/金鯉躍門_日報_2026-09.xlsx
+++ b/ops-data/金鯉躍門_日報_2026-09.xlsx
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>σ ÷ √等效轉數。σ 為 PAR 表的單局標準差（× 總押注）</t>
+          <t>σ ÷ √等效轉數。σ 為 數值規格表的單局標準差（× 總押注）</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>遊戲設定（來源：games 資料表／PAR 表）</t>
+          <t>遊戲設定（來源：games 資料表／數值規格表）</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>理論 RTP、σ、觸發率依 PAR 表規格；v1.3 的規格與 v1.2 相同，實際上線版本的設定錯誤不會反映在理論值上，這正是要靠報表抓出來的差異。</t>
+          <t>理論 RTP、σ、觸發率依 數值規格表；v1.3 的規格與 v1.2 相同，實際上線版本的設定錯誤不會反映在理論值上，這正是要靠報表抓出來的差異。</t>
         </is>
       </c>
     </row>

--- a/ops-data/金鯉躍門_日報_2026-09.xlsx
+++ b/ops-data/金鯉躍門_日報_2026-09.xlsx
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>σ ÷ √等效轉數。σ 為 數值規格表的單局標準差（× 總押注）</t>
+          <t>σ ÷ √等效轉數。σ 為數值規格表的單局標準差（× 總押注）</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>理論 RTP、σ、觸發率依 數值規格表；v1.3 的規格與 v1.2 相同，實際上線版本的設定錯誤不會反映在理論值上，這正是要靠報表抓出來的差異。</t>
+          <t>理論 RTP、σ、觸發率依數值規格表；v1.3 的規格與 v1.2 相同，實際上線版本的設定錯誤不會反映在理論值上，這正是要靠報表抓出來的差異。</t>
         </is>
       </c>
     </row>
